--- a/data/trans_camb/P19C05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C05-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 5,1</t>
+          <t>-4,04; 5,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,83; -1,1</t>
+          <t>-10,64; -1,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,87; -4,26</t>
+          <t>-13,46; -4,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 7,31</t>
+          <t>-0,8; 7,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,22; -4,4</t>
+          <t>-13,3; -4,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 0,2</t>
+          <t>-6,97; 0,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 5,4</t>
+          <t>-0,72; 5,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,18; -4,62</t>
+          <t>-10,89; -4,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -2,76</t>
+          <t>-8,59; -2,71</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 19,86</t>
+          <t>-13,71; 22,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,39; -4,39</t>
+          <t>-37,89; -5,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,16; -16,7</t>
+          <t>-45,31; -16,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 26,34</t>
+          <t>-2,4; 25,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,32; -15,6</t>
+          <t>-41,16; -14,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 0,66</t>
+          <t>-21,37; 1,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 19,66</t>
+          <t>-2,41; 19,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,79; -16,68</t>
+          <t>-36,17; -15,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,26; -10,16</t>
+          <t>-27,86; -9,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,29</t>
+          <t>0,95; 5,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,16</t>
+          <t>-0,93; 3,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,56</t>
+          <t>-2,56; 2,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,07</t>
+          <t>-0,39; 4,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,2</t>
+          <t>-1,29; 2,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 0,64</t>
+          <t>-3,69; 0,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,97</t>
+          <t>1,01; 4,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,48</t>
+          <t>-0,35; 2,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,1</t>
+          <t>-2,27; 1,04</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 82,55</t>
+          <t>11,24; 87,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 49,59</t>
+          <t>-10,94; 50,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,28; 40,49</t>
+          <t>-29,27; 40,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 55,26</t>
+          <t>-4,27; 58,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 44,17</t>
+          <t>-13,71; 37,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 7,75</t>
+          <t>-39,04; 6,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,89; 53,96</t>
+          <t>11,79; 57,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 34,13</t>
+          <t>-4,0; 36,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 14,66</t>
+          <t>-26,41; 14,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 2,49</t>
+          <t>-6,09; 2,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,23</t>
+          <t>-7,1; 0,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 1,39</t>
+          <t>-5,99; 1,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 2,1</t>
+          <t>-6,36; 1,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 1,73</t>
+          <t>-6,34; 1,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,95</t>
+          <t>-5,83; 0,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,11</t>
+          <t>-4,76; 0,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 0,01</t>
+          <t>-5,53; -0,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,06</t>
+          <t>-4,88; -0,09</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,1; 27,37</t>
+          <t>-46,95; 34,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,75; 13,03</t>
+          <t>-54,57; 13,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,44; 18,01</t>
+          <t>-45,52; 14,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,58; 28,29</t>
+          <t>-53,52; 27,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,58; 22,66</t>
+          <t>-52,02; 23,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,1; 12,86</t>
+          <t>-48,87; 13,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 11,44</t>
+          <t>-41,67; 8,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,62; -0,26</t>
+          <t>-46,95; 0,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-41,77; 1,49</t>
+          <t>-42,04; -1,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,35</t>
+          <t>-0,49; 3,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,8; -0,95</t>
+          <t>-4,95; -1,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,51; -2,37</t>
+          <t>-6,89; -2,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,1</t>
+          <t>0,01; 4,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -2,65</t>
+          <t>-6,28; -2,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -3,09</t>
+          <t>-7,35; -3,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,22</t>
+          <t>0,33; 3,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,05; -2,24</t>
+          <t>-5,08; -2,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -3,22</t>
+          <t>-6,16; -3,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 26,34</t>
+          <t>-3,43; 25,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,52; -7,8</t>
+          <t>-33,73; -8,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,44; -18,08</t>
+          <t>-47,41; -18,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,44; 26,8</t>
+          <t>-0,09; 27,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,2; -17,44</t>
+          <t>-37,55; -18,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,3; -20,72</t>
+          <t>-43,92; -21,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,02; 22,71</t>
+          <t>2,05; 21,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,47; -15,83</t>
+          <t>-32,01; -16,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,19; -22,85</t>
+          <t>-39,48; -22,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C05-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-8,9</t>
+          <t>-9,47</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,27</t>
+          <t>-3,54</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,48</t>
+          <t>-5,92</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 5,63</t>
+          <t>-3,89; 5,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,64; -1,2</t>
+          <t>-11,07; -1,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,46; -4,11</t>
+          <t>-13,46; -4,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 7,23</t>
+          <t>-0,79; 7,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,3; -4,05</t>
+          <t>-13,07; -3,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 0,43</t>
+          <t>-7,2; -0,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,33</t>
+          <t>-0,92; 5,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,89; -4,23</t>
+          <t>-10,79; -4,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,59; -2,71</t>
+          <t>-9,0; -2,79</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-32,84%</t>
+          <t>-34,94%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-10,91%</t>
+          <t>-11,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-19,06%</t>
+          <t>-20,56%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 22,56</t>
+          <t>-13,16; 23,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,89; -5,14</t>
+          <t>-37,82; -3,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,31; -16,5</t>
+          <t>-46,43; -20,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 25,56</t>
+          <t>-2,53; 28,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,16; -14,04</t>
+          <t>-41,59; -14,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 1,99</t>
+          <t>-22,78; -0,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 19,77</t>
+          <t>-2,92; 20,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,17; -15,68</t>
+          <t>-36,03; -15,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-27,86; -9,81</t>
+          <t>-29,39; -10,3</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>0,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,42</t>
+          <t>0,84; 5,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,34</t>
+          <t>-0,79; 3,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,65</t>
+          <t>-0,13; 3,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,25</t>
+          <t>-0,35; 4,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,77</t>
+          <t>-1,33; 2,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,51</t>
+          <t>-1,91; 1,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,16</t>
+          <t>0,98; 4,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,61</t>
+          <t>-0,41; 2,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,04</t>
+          <t>-0,52; 2,11</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-15,15%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-4,94%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,24; 87,96</t>
+          <t>9,41; 76,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 50,05</t>
+          <t>-9,36; 49,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,27; 40,32</t>
+          <t>-1,48; 60,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 58,59</t>
+          <t>-3,8; 55,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 37,68</t>
+          <t>-13,6; 39,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 6,3</t>
+          <t>-19,83; 24,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,79; 57,1</t>
+          <t>11,01; 58,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 36,87</t>
+          <t>-4,71; 37,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 14,51</t>
+          <t>-5,74; 30,35</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-2,46</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,44</t>
+          <t>-2,62</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-2,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 2,77</t>
+          <t>-6,29; 2,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 0,72</t>
+          <t>-7,02; 0,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 1,16</t>
+          <t>-6,66; 0,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 1,99</t>
+          <t>-6,03; 1,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 1,36</t>
+          <t>-6,24; 1,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 0,9</t>
+          <t>-6,27; 0,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,79</t>
+          <t>-4,67; 1,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -0,05</t>
+          <t>-5,35; 0,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,09</t>
+          <t>-5,23; -0,14</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-20,96%</t>
+          <t>-22,82%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-25,65%</t>
+          <t>-27,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-23,5%</t>
+          <t>-25,36%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 34,8</t>
+          <t>-46,9; 33,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,57; 13,34</t>
+          <t>-52,94; 15,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-45,52; 14,62</t>
+          <t>-48,81; 10,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,52; 27,7</t>
+          <t>-50,37; 26,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,02; 23,44</t>
+          <t>-53,41; 20,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 13,67</t>
+          <t>-51,01; 8,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,67; 8,82</t>
+          <t>-40,2; 15,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 0,82</t>
+          <t>-46,14; 0,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-42,04; -1,28</t>
+          <t>-41,8; -0,23</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,03</t>
+          <t>-3,2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,04</t>
+          <t>-4,1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,58</t>
+          <t>-3,7</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,24</t>
+          <t>-0,54; 3,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,95; -1,09</t>
+          <t>-4,71; -1,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -2,45</t>
+          <t>-4,98; -1,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,17</t>
+          <t>-0,11; 3,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,28; -2,72</t>
+          <t>-6,27; -2,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,35; -3,21</t>
+          <t>-5,79; -2,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,07</t>
+          <t>0,28; 3,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,08; -2,43</t>
+          <t>-5,1; -2,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,16; -3,21</t>
+          <t>-4,94; -2,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-29,65%</t>
+          <t>-23,58%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-31,25%</t>
+          <t>-25,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-30,68%</t>
+          <t>-24,75%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 25,53</t>
+          <t>-3,76; 26,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,73; -8,93</t>
+          <t>-32,53; -8,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,41; -18,96</t>
+          <t>-33,68; -12,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 27,24</t>
+          <t>-0,54; 26,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,55; -18,2</t>
+          <t>-36,92; -16,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,92; -21,38</t>
+          <t>-33,27; -16,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,05; 21,34</t>
+          <t>1,81; 22,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,01; -16,83</t>
+          <t>-32,72; -16,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,48; -22,77</t>
+          <t>-31,18; -17,43</t>
         </is>
       </c>
     </row>
